--- a/Bitácora de Actividades para EFSRT en IES.xlsx
+++ b/Bitácora de Actividades para EFSRT en IES.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo.Z50\Documents\Ciber 2024-1\EFSRTII\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo.Z50\Documents\Ciber 2024-1\POOII\Workspace\ProyectoEFSRT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{451017BA-995C-42B4-A2FB-912A5A8D3792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5807B6B6-E635-4446-8EC0-7F21759BCE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="G43haX0B3YNA2Aeuv05iq6D6DByn0iKwf1wKbHLAW5poYSwzX5zOpE3sSXz9bCPM36JkOtAlHOujh13WVFUKHQ==" workbookSaltValue="coeSergEaNiod+kXFJRaBg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{E069488D-1A23-4E38-BD88-C358EEB7BFCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E069488D-1A23-4E38-BD88-C358EEB7BFCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitácora EFSRT dentro del IEST" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="194">
   <si>
     <t>Monitoreo</t>
   </si>
@@ -620,6 +620,18 @@
   </si>
   <si>
     <t>implementacion de DAO</t>
+  </si>
+  <si>
+    <t>Implementacion de vistas</t>
+  </si>
+  <si>
+    <t>Implementacion de controlers y BPMN</t>
+  </si>
+  <si>
+    <t>Informe  y pruebas</t>
+  </si>
+  <si>
+    <t>Video y detalles finales</t>
   </si>
 </sst>
 </file>
@@ -887,14 +899,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -933,12 +951,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1332,17 +1344,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="26" t="s">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
@@ -1351,17 +1363,17 @@
       <c r="O1" s="13"/>
     </row>
     <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="27" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
@@ -1370,17 +1382,17 @@
       <c r="O2" s="14"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="28" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
@@ -1404,13 +1416,13 @@
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -1462,69 +1474,69 @@
       <c r="A10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="29" t="s">
+      <c r="B15" s="32"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="31" t="s">
+      <c r="E15" s="31"/>
+      <c r="F15" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="22" t="s">
+      <c r="G15" s="33"/>
+      <c r="H15" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="I15" s="23"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1559,10 +1571,10 @@
       <c r="A17" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="17">
         <v>0.875</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="17">
         <v>0.91666666666666663</v>
       </c>
       <c r="D17" s="3"/>
@@ -1574,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4"/>
-      <c r="I17" s="32">
+      <c r="I17" s="16">
         <v>45455</v>
       </c>
     </row>
@@ -1584,10 +1596,10 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="33">
+      <c r="D18" s="17">
         <v>0.83333333333333337</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="17">
         <v>0.91666666666666663</v>
       </c>
       <c r="F18" s="3">
@@ -1597,7 +1609,7 @@
         <v>0.75</v>
       </c>
       <c r="H18" s="4"/>
-      <c r="I18" s="32">
+      <c r="I18" s="16">
         <v>45465</v>
       </c>
     </row>
@@ -1607,20 +1619,20 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="33">
-        <v>0.875</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="D19" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E19" s="17">
         <v>0.91666666666666663</v>
       </c>
       <c r="F19" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="11">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H19" s="4"/>
-      <c r="I19" s="32">
+      <c r="I19" s="16">
         <v>45466</v>
       </c>
     </row>
@@ -1630,66 +1642,113 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="33">
+      <c r="D20" s="17">
         <v>0.91666666666666663</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="17">
         <v>0.9375</v>
       </c>
       <c r="F20" s="3">
         <v>0.5</v>
       </c>
       <c r="G20" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="16">
+        <v>45466</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="16">
+        <v>45469</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="16">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2</v>
+      </c>
+      <c r="G23" s="11">
         <v>0.9</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="32">
-        <v>45466</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="11"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="16">
+        <v>45447</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="11"/>
+      <c r="A24" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
       <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="16">
+        <v>45448</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
@@ -2704,27 +2763,21 @@
       <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="19" t="s">
+      <c r="A117" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B117" s="20"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="21"/>
+      <c r="B117" s="22"/>
+      <c r="C117" s="22"/>
+      <c r="D117" s="22"/>
+      <c r="E117" s="23"/>
       <c r="F117" s="12">
         <f>SUM(F17:F116)</f>
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A16:F16" xr:uid="{CD90EDCD-9C5D-4652-9687-07882510B60A}"/>
   <mergeCells count="19">
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="A117:E117"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="A14:I14"/>
@@ -2738,6 +2791,12 @@
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="B6:F6"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="E17">
